--- a/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.33</v>
@@ -2876,7 +2876,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.42</v>
@@ -7672,7 +7672,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR33" t="n">
         <v>1.66</v>
@@ -11596,7 +11596,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR51" t="n">
         <v>1.98</v>
@@ -14427,7 +14427,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.64</v>
@@ -15517,7 +15517,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.5</v>
@@ -15956,7 +15956,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR71" t="n">
         <v>1.23</v>
@@ -19223,7 +19223,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.33</v>
@@ -22278,7 +22278,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR100" t="n">
         <v>1.16</v>
@@ -24237,7 +24237,7 @@
         <v>1</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.09</v>
@@ -25984,7 +25984,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR117" t="n">
         <v>1.68</v>
@@ -27507,7 +27507,7 @@
         <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.73</v>
@@ -28818,7 +28818,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR130" t="n">
         <v>1.53</v>
@@ -31870,7 +31870,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR144" t="n">
         <v>1.7</v>
@@ -34922,7 +34922,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR158" t="n">
         <v>1.56</v>
@@ -36009,7 +36009,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.33</v>
@@ -37971,7 +37971,7 @@
         <v>1.56</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.42</v>
@@ -39282,7 +39282,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR178" t="n">
         <v>1.72</v>
@@ -42988,7 +42988,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR195" t="n">
         <v>1.58</v>
@@ -43421,7 +43421,7 @@
         <v>1.1</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.25</v>
@@ -46270,31 +46270,31 @@
         <v>2.98</v>
       </c>
       <c r="AU210" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV210" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX210" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY210" t="n">
         <v>8</v>
       </c>
       <c r="AZ210" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA210" t="n">
         <v>3</v>
       </c>
       <c r="BB210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC210" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD210" t="n">
         <v>1.49</v>
@@ -46334,6 +46334,224 @@
       </c>
       <c r="BP210" t="n">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8193719</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>46081.625</v>
+      </c>
+      <c r="F211" t="n">
+        <v>24</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>União de Leiria</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Portimonense</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S211" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U211" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X211" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.33</v>
@@ -1568,7 +1568,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.33</v>
@@ -3094,7 +3094,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.82</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.42</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR20" t="n">
         <v>1.74</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.33</v>
@@ -6582,7 +6582,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR28" t="n">
         <v>1.65</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.33</v>
@@ -7236,7 +7236,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR31" t="n">
         <v>1.38</v>
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.5</v>
@@ -7887,10 +7887,10 @@
         <v>3</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR34" t="n">
         <v>1.77</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.25</v>
@@ -8544,7 +8544,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR37" t="n">
         <v>2.14</v>
@@ -8762,7 +8762,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR38" t="n">
         <v>1.3</v>
@@ -11160,7 +11160,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR49" t="n">
         <v>2.03</v>
@@ -11375,10 +11375,10 @@
         <v>0.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR50" t="n">
         <v>1.3</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.33</v>
@@ -11811,10 +11811,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR52" t="n">
         <v>2.06</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.33</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.25</v>
@@ -14430,7 +14430,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR64" t="n">
         <v>1.18</v>
@@ -14648,7 +14648,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR65" t="n">
         <v>1.16</v>
@@ -14863,7 +14863,7 @@
         <v>0.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.25</v>
@@ -15084,7 +15084,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR67" t="n">
         <v>1.45</v>
@@ -15302,7 +15302,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR68" t="n">
         <v>1.75</v>
@@ -15738,7 +15738,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR70" t="n">
         <v>1.8</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.33</v>
@@ -16171,10 +16171,10 @@
         <v>0.67</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR72" t="n">
         <v>1.99</v>
@@ -16389,7 +16389,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.33</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ74" t="n">
         <v>1</v>
@@ -18569,10 +18569,10 @@
         <v>1.25</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -18790,7 +18790,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR84" t="n">
         <v>1.22</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.5</v>
@@ -19444,7 +19444,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR87" t="n">
         <v>1.78</v>
@@ -19659,10 +19659,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR88" t="n">
         <v>1.9</v>
@@ -19877,7 +19877,7 @@
         <v>2.5</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.33</v>
@@ -20095,7 +20095,7 @@
         <v>2.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.42</v>
@@ -20316,7 +20316,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR91" t="n">
         <v>1.82</v>
@@ -22929,7 +22929,7 @@
         <v>1.14</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ103" t="n">
         <v>1</v>
@@ -23368,7 +23368,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR105" t="n">
         <v>1.18</v>
@@ -23804,7 +23804,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ107" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR107" t="n">
         <v>1.88</v>
@@ -24240,7 +24240,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR109" t="n">
         <v>1.66</v>
@@ -24455,10 +24455,10 @@
         <v>0.4</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR110" t="n">
         <v>1.49</v>
@@ -24891,7 +24891,7 @@
         <v>1.5</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.33</v>
@@ -25766,7 +25766,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR116" t="n">
         <v>2.18</v>
@@ -26199,7 +26199,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.33</v>
@@ -26635,7 +26635,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.33</v>
@@ -27510,7 +27510,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR124" t="n">
         <v>1.66</v>
@@ -27725,7 +27725,7 @@
         <v>1.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.33</v>
@@ -28379,10 +28379,10 @@
         <v>1.5</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR128" t="n">
         <v>1.43</v>
@@ -28600,7 +28600,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR129" t="n">
         <v>1.88</v>
@@ -29251,7 +29251,7 @@
         <v>0.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.82</v>
@@ -29690,7 +29690,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR134" t="n">
         <v>1.59</v>
@@ -29905,7 +29905,7 @@
         <v>1.29</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.33</v>
@@ -30123,7 +30123,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.42</v>
@@ -30562,7 +30562,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR138" t="n">
         <v>1.69</v>
@@ -30777,10 +30777,10 @@
         <v>1</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR139" t="n">
         <v>1.84</v>
@@ -30995,7 +30995,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.33</v>
@@ -31216,7 +31216,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR141" t="n">
         <v>1.44</v>
@@ -31431,7 +31431,7 @@
         <v>1.5</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.33</v>
@@ -31652,7 +31652,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR143" t="n">
         <v>1.65</v>
@@ -31867,7 +31867,7 @@
         <v>1.29</v>
       </c>
       <c r="AP144" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.33</v>
@@ -32303,7 +32303,7 @@
         <v>0.75</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.82</v>
@@ -33178,7 +33178,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR150" t="n">
         <v>1.79</v>
@@ -33396,7 +33396,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ151" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR151" t="n">
         <v>1.63</v>
@@ -34265,7 +34265,7 @@
         <v>1.44</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.33</v>
@@ -34483,10 +34483,10 @@
         <v>0.75</v>
       </c>
       <c r="AP156" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR156" t="n">
         <v>1.84</v>
@@ -34919,7 +34919,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.33</v>
@@ -35358,7 +35358,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ160" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR160" t="n">
         <v>1.58</v>
@@ -35573,7 +35573,7 @@
         <v>1</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.25</v>
@@ -36227,7 +36227,7 @@
         <v>1.44</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.33</v>
@@ -36448,7 +36448,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR165" t="n">
         <v>1.54</v>
@@ -36666,7 +36666,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR166" t="n">
         <v>1.8</v>
@@ -36884,7 +36884,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR167" t="n">
         <v>1.57</v>
@@ -38192,7 +38192,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR173" t="n">
         <v>2.13</v>
@@ -38407,7 +38407,7 @@
         <v>1.22</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.5</v>
@@ -38843,7 +38843,7 @@
         <v>1.6</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.42</v>
@@ -39061,7 +39061,7 @@
         <v>0.89</v>
       </c>
       <c r="AP177" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.25</v>
@@ -39500,7 +39500,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR179" t="n">
         <v>1.61</v>
@@ -39715,10 +39715,10 @@
         <v>2.67</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ180" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR180" t="n">
         <v>1.88</v>
@@ -40372,7 +40372,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR183" t="n">
         <v>1.55</v>
@@ -41462,7 +41462,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR188" t="n">
         <v>1.6</v>
@@ -41677,7 +41677,7 @@
         <v>1.4</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.42</v>
@@ -41895,7 +41895,7 @@
         <v>1.6</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.33</v>
@@ -42113,10 +42113,10 @@
         <v>0.7</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR191" t="n">
         <v>1.73</v>
@@ -42331,7 +42331,7 @@
         <v>1.2</v>
       </c>
       <c r="AP192" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.5</v>
@@ -42552,7 +42552,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR193" t="n">
         <v>2.13</v>
@@ -42770,7 +42770,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ194" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AR194" t="n">
         <v>1.71</v>
@@ -43203,7 +43203,7 @@
         <v>1.45</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.42</v>
@@ -43639,10 +43639,10 @@
         <v>1.9</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR198" t="n">
         <v>1.44</v>
@@ -44078,7 +44078,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR200" t="n">
         <v>1.57</v>
@@ -46552,6 +46552,1096 @@
       </c>
       <c r="BP211" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8193942</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>46082.33333333334</v>
+      </c>
+      <c r="F212" t="n">
+        <v>24</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Lusitania Lourosa</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
+        <v>2</v>
+      </c>
+      <c r="M212" t="n">
+        <v>1</v>
+      </c>
+      <c r="N212" t="n">
+        <v>3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>['13', '89']</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S212" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V212" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X212" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8193704</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F213" t="n">
+        <v>24</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>CS Marítimo</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>3</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['40', '90+6', '90+8']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>3</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S213" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V213" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X213" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8193667</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46082.52083333334</v>
+      </c>
+      <c r="F214" t="n">
+        <v>24</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Paços de Ferreira</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U214" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V214" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X214" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8193705</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46082.625</v>
+      </c>
+      <c r="F215" t="n">
+        <v>24</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>FC Penafiel</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Benfica II</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S215" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U215" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X215" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8193817</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46083.625</v>
+      </c>
+      <c r="F216" t="n">
+        <v>24</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>CD Feirense</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Felgueiras 1932</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>3</v>
+      </c>
+      <c r="R216" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S216" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V216" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X216" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
@@ -47584,16 +47584,16 @@
         <v>1</v>
       </c>
       <c r="AW216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX216" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ216" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA216" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
@@ -5575,7 +5575,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>8193662</v>
+        <v>8193810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5595,197 +5595,197 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '17']</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U24" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V24" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="W24" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB24" t="n">
         <v>7</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="BC24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BI24" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="BJ24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM24" t="n">
         <v>1.91</v>
       </c>
-      <c r="AH24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>2.03</v>
-      </c>
       <c r="BN24" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="BP24" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="25">
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>8193810</v>
+        <v>8193662</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5813,197 +5813,197 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>2</v>
       </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>['6', '17']</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="AK25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.4</v>
       </c>
-      <c r="U25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS25" t="n">
         <v>1.03</v>
       </c>
-      <c r="AD25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AT25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AK25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AS25" t="n">
+      <c r="BE25" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BK25" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BL25" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="BN25" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BO25" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="BP25" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="26">
@@ -10807,7 +10807,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>8193926</v>
+        <v>8193848</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -10827,197 +10827,197 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>['58', '90+3', '90']</t>
+          <t>['66', '90']</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>['45+3', '61', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R48" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S48" t="n">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="T48" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="U48" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="V48" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="W48" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AD48" t="n">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK48" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.33</v>
       </c>
       <c r="AL48" t="n">
         <v>1.32</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AN48" t="n">
         <v>0.5</v>
       </c>
       <c r="AO48" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.42</v>
+        <v>0.75</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.57</v>
+        <v>1.3</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AT48" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="AU48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AV48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AW48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY48" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ48" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC48" t="n">
         <v>12</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.94</v>
+        <v>2.79</v>
       </c>
       <c r="BE48" t="n">
-        <v>6.45</v>
+        <v>7.5</v>
       </c>
       <c r="BF48" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BH48" t="n">
-        <v>3.56</v>
+        <v>4.08</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BJ48" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="BK48" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="BL48" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="BM48" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="BN48" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BO48" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="BP48" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="49">
@@ -11243,7 +11243,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>8193848</v>
+        <v>8193926</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -11263,197 +11263,197 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>['66', '90']</t>
+          <t>['58', '90+3', '90']</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3', '61', '76']</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S50" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="T50" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="U50" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="V50" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="W50" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="AC50" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AD50" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF50" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL50" t="n">
         <v>1.32</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AN50" t="n">
         <v>0.5</v>
       </c>
       <c r="AO50" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.75</v>
+        <v>1.42</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.3</v>
+        <v>2.57</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.69</v>
+        <v>4.03</v>
       </c>
       <c r="AU50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY50" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AZ50" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BA50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC50" t="n">
         <v>12</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.79</v>
+        <v>1.94</v>
       </c>
       <c r="BE50" t="n">
-        <v>7.5</v>
+        <v>6.45</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BH50" t="n">
-        <v>4.08</v>
+        <v>3.56</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BJ50" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BL50" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="BM50" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="BN50" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BO50" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="BP50" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="51">
@@ -13205,7 +13205,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>8193739</v>
+        <v>8193663</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -13225,197 +13225,197 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
         <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>['3', '81']</t>
+          <t>['12', '45+6']</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>['67', '90+2']</t>
+          <t>['63', '70', '73']</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R59" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S59" t="n">
-        <v>3.44</v>
+        <v>2.8</v>
       </c>
       <c r="T59" t="n">
         <v>1.4</v>
       </c>
       <c r="U59" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V59" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X59" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA59" t="n">
         <v>3</v>
       </c>
-      <c r="W59" t="n">
+      <c r="AB59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO59" t="n">
         <v>1.33</v>
       </c>
-      <c r="X59" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AP59" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.82</v>
+        <v>1.42</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.75</v>
+        <v>1.64</v>
       </c>
       <c r="AT59" t="n">
-        <v>1.98</v>
+        <v>2.74</v>
       </c>
       <c r="AU59" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV59" t="n">
         <v>4</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>5</v>
       </c>
       <c r="AW59" t="n">
         <v>6</v>
       </c>
       <c r="AX59" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY59" t="n">
         <v>11</v>
       </c>
-      <c r="AY59" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ59" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB59" t="n">
         <v>5</v>
       </c>
-      <c r="BB59" t="n">
-        <v>3</v>
-      </c>
       <c r="BC59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD59" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="BE59" t="n">
-        <v>6.45</v>
+        <v>8.5</v>
       </c>
       <c r="BF59" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BH59" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BI59" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BJ59" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="BK59" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BL59" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="BM59" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="BN59" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BO59" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="BP59" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="60">
@@ -13423,7 +13423,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>8193663</v>
+        <v>8193739</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -13443,197 +13443,197 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>['3', '81']</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>['67', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
         <v>3</v>
       </c>
-      <c r="N60" t="n">
-        <v>5</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>['12', '45+6']</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>['63', '70', '73']</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R60" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S60" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="T60" t="n">
         <v>1.4</v>
       </c>
       <c r="U60" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V60" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="W60" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X60" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z60" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA60" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA60" t="n">
-        <v>3</v>
-      </c>
       <c r="AB60" t="n">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD60" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL60" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO60" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.42</v>
+        <v>0.82</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.64</v>
+        <v>0.75</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.74</v>
+        <v>1.98</v>
       </c>
       <c r="AU60" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV60" t="n">
         <v>5</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>4</v>
       </c>
       <c r="AW60" t="n">
         <v>6</v>
       </c>
       <c r="AX60" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA60" t="n">
         <v>5</v>
       </c>
-      <c r="AY60" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>1</v>
-      </c>
       <c r="BB60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD60" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="BE60" t="n">
-        <v>8.5</v>
+        <v>6.45</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BH60" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BI60" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BJ60" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="BK60" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="BL60" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="BM60" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="BN60" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO60" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="BP60" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="61">
@@ -15385,7 +15385,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>8193860</v>
+        <v>8193937</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -15405,80 +15405,80 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
         <v>4</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['41', '45+9', '54', '64']</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>['20', '60', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="R69" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T69" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U69" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V69" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="W69" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X69" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="Y69" t="n">
         <v>1.06</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AA69" t="n">
         <v>3.1</v>
       </c>
       <c r="AB69" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AD69" t="n">
         <v>8</v>
@@ -15487,115 +15487,115 @@
         <v>1.36</v>
       </c>
       <c r="AF69" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="AG69" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AJ69" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AL69" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AM69" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AN69" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO69" t="n">
-        <v>0.33</v>
+        <v>2</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.62</v>
+        <v>3.19</v>
       </c>
       <c r="AU69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX69" t="n">
         <v>6</v>
       </c>
-      <c r="AW69" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX69" t="n">
+      <c r="AY69" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ69" t="n">
         <v>8</v>
       </c>
-      <c r="AY69" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ69" t="n">
-        <v>14</v>
-      </c>
       <c r="BA69" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BB69" t="n">
         <v>2</v>
       </c>
       <c r="BC69" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD69" t="n">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="BE69" t="n">
-        <v>6.75</v>
+        <v>6.35</v>
       </c>
       <c r="BF69" t="n">
-        <v>3.06</v>
+        <v>2.19</v>
       </c>
       <c r="BG69" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BH69" t="n">
-        <v>3.92</v>
+        <v>3.38</v>
       </c>
       <c r="BI69" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="BJ69" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="BK69" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="BL69" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="BM69" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="BN69" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="BO69" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="BP69" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="70">
@@ -15603,7 +15603,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>8193937</v>
+        <v>8193860</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -15623,80 +15623,80 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
         <v>4</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>['41', '45+9', '54', '64']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '60', '63']</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="R70" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S70" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T70" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="U70" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="W70" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X70" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="Y70" t="n">
         <v>1.06</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AA70" t="n">
         <v>3.1</v>
       </c>
       <c r="AB70" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD70" t="n">
         <v>8</v>
@@ -15705,115 +15705,115 @@
         <v>1.36</v>
       </c>
       <c r="AF70" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ70" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AK70" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AL70" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AM70" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AN70" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO70" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AQ70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR70" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR70" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AS70" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.19</v>
+        <v>2.62</v>
       </c>
       <c r="AU70" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW70" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY70" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ70" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BB70" t="n">
         <v>2</v>
       </c>
       <c r="BC70" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD70" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="BE70" t="n">
-        <v>6.35</v>
+        <v>6.75</v>
       </c>
       <c r="BF70" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="BG70" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BH70" t="n">
-        <v>3.38</v>
+        <v>3.92</v>
       </c>
       <c r="BI70" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="BJ70" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="BK70" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="BL70" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="BM70" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="BN70" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="BO70" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="BP70" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="71">
@@ -25413,7 +25413,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>8193858</v>
+        <v>8193940</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -25433,197 +25433,197 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="I115" t="n">
         <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
         <v>2</v>
       </c>
       <c r="M115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>['26', '54']</t>
+          <t>['41', '55']</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>['29', '45+8', '62', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="R115" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="S115" t="n">
-        <v>3.73</v>
+        <v>5.39</v>
       </c>
       <c r="T115" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="U115" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="V115" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="W115" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="X115" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AA115" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AB115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AD115" t="n">
-        <v>7.9</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AG115" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM115" t="n">
         <v>2.15</v>
       </c>
-      <c r="AH115" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK115" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AL115" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM115" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AN115" t="n">
-        <v>1.29</v>
+        <v>0.83</v>
       </c>
       <c r="AO115" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.25</v>
+        <v>0.67</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="AU115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
         <v>17</v>
       </c>
       <c r="AX115" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AY115" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ115" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA115" t="n">
         <v>8</v>
       </c>
-      <c r="BA115" t="n">
-        <v>9</v>
-      </c>
       <c r="BB115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC115" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BD115" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BE115" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF115" t="n">
-        <v>2.74</v>
+        <v>3.63</v>
       </c>
       <c r="BG115" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BH115" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BI115" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BJ115" t="n">
-        <v>2.63</v>
+        <v>3.17</v>
       </c>
       <c r="BK115" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="BL115" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="BM115" t="n">
-        <v>2.13</v>
+        <v>1.86</v>
       </c>
       <c r="BN115" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="BO115" t="n">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="BP115" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="116">
@@ -25631,7 +25631,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>8193940</v>
+        <v>8193858</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -25651,197 +25651,197 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="I116" t="n">
         <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L116" t="n">
         <v>2</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>['41', '55']</t>
+          <t>['26', '54']</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '45+8', '62', '68']</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="R116" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="S116" t="n">
-        <v>5.39</v>
+        <v>3.73</v>
       </c>
       <c r="T116" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="U116" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="V116" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="W116" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="X116" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y116" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP116" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z116" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB116" t="n">
+      <c r="AQ116" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU116" t="n">
         <v>5</v>
       </c>
-      <c r="AC116" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="AE116" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF116" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG116" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH116" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AI116" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK116" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL116" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM116" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AN116" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AO116" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP116" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ116" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AR116" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS116" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AT116" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU116" t="n">
-        <v>7</v>
-      </c>
       <c r="AV116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW116" t="n">
         <v>17</v>
       </c>
       <c r="AX116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA116" t="n">
         <v>9</v>
       </c>
-      <c r="AY116" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ116" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>8</v>
-      </c>
       <c r="BB116" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BC116" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BD116" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="BE116" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF116" t="n">
-        <v>3.63</v>
+        <v>2.74</v>
       </c>
       <c r="BG116" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BH116" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="BI116" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="BJ116" t="n">
-        <v>3.17</v>
+        <v>2.63</v>
       </c>
       <c r="BK116" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="BL116" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="BM116" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="BN116" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="BO116" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="BP116" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="117">
@@ -26721,7 +26721,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>8193729</v>
+        <v>8193665</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -26741,197 +26741,197 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="I121" t="n">
         <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['9', '47']</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4', '54', '73']</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>2.76</v>
+        <v>4.4</v>
       </c>
       <c r="R121" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S121" t="n">
-        <v>4.08</v>
+        <v>2.45</v>
       </c>
       <c r="T121" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U121" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="V121" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="W121" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X121" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y121" t="n">
         <v>1.03</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="AA121" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB121" t="n">
-        <v>3.41</v>
+        <v>1.83</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD121" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW121" t="n">
         <v>9</v>
       </c>
-      <c r="AE121" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF121" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG121" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK121" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL121" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM121" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AN121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP121" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR121" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AS121" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AT121" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU121" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW121" t="n">
-        <v>5</v>
-      </c>
       <c r="AX121" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AY121" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ121" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA121" t="n">
         <v>6</v>
       </c>
       <c r="BB121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC121" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD121" t="n">
-        <v>1.6</v>
+        <v>2.49</v>
       </c>
       <c r="BE121" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF121" t="n">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
       <c r="BG121" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BH121" t="n">
-        <v>3.94</v>
+        <v>3.61</v>
       </c>
       <c r="BI121" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="BJ121" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="BK121" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="BL121" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="BM121" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="BN121" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BO121" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="BP121" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="122">
@@ -26939,7 +26939,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>8193665</v>
+        <v>8193729</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -26959,197 +26959,197 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="I122" t="n">
         <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R122" t="n">
         <v>2</v>
       </c>
-      <c r="L122" t="n">
-        <v>2</v>
-      </c>
-      <c r="M122" t="n">
+      <c r="S122" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U122" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V122" t="n">
         <v>3</v>
       </c>
-      <c r="N122" t="n">
-        <v>5</v>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>['9', '47']</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>['45+4', '54', '73']</t>
-        </is>
-      </c>
-      <c r="Q122" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R122" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S122" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T122" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U122" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V122" t="n">
-        <v>2.95</v>
-      </c>
       <c r="W122" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X122" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Y122" t="n">
         <v>1.03</v>
       </c>
       <c r="Z122" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU122" t="n">
         <v>4</v>
       </c>
-      <c r="AA122" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG122" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AK122" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL122" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AM122" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN122" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO122" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AP122" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ122" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR122" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AS122" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AT122" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AU122" t="n">
+      <c r="AV122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW122" t="n">
         <v>5</v>
       </c>
-      <c r="AV122" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW122" t="n">
+      <c r="AX122" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY122" t="n">
         <v>9</v>
       </c>
-      <c r="AX122" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY122" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ122" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA122" t="n">
         <v>6</v>
       </c>
       <c r="BB122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC122" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD122" t="n">
-        <v>2.49</v>
+        <v>1.6</v>
       </c>
       <c r="BE122" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF122" t="n">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
       <c r="BG122" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BH122" t="n">
-        <v>3.61</v>
+        <v>3.94</v>
       </c>
       <c r="BI122" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="BJ122" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="BK122" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BL122" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="BM122" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="BN122" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BO122" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="BP122" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="123">
@@ -28901,7 +28901,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>8193758</v>
+        <v>8193834</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -28921,12 +28921,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -28942,10 +28942,10 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -28954,164 +28954,164 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>3.12</v>
+        <v>2.61</v>
       </c>
       <c r="R131" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S131" t="n">
-        <v>3.82</v>
+        <v>4.85</v>
       </c>
       <c r="T131" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="U131" t="n">
-        <v>2.76</v>
+        <v>2.41</v>
       </c>
       <c r="V131" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="W131" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X131" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Z131" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="AA131" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB131" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU131" t="n">
         <v>3</v>
       </c>
-      <c r="AC131" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD131" t="n">
+      <c r="AV131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX131" t="n">
         <v>8</v>
       </c>
-      <c r="AE131" t="n">
+      <c r="AY131" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BP131" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ131" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK131" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL131" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AM131" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AN131" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO131" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AP131" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AQ131" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR131" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS131" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT131" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AU131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW131" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX131" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY131" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ131" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA131" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB131" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC131" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD131" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BE131" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF131" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG131" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BH131" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI131" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BJ131" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BK131" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BL131" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BM131" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BN131" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BO131" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BP131" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="132">
@@ -29119,7 +29119,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>8193834</v>
+        <v>8193758</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -29139,12 +29139,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -29160,10 +29160,10 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -29172,164 +29172,164 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>2.61</v>
+        <v>3.12</v>
       </c>
       <c r="R132" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S132" t="n">
-        <v>4.85</v>
+        <v>3.82</v>
       </c>
       <c r="T132" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="U132" t="n">
-        <v>2.41</v>
+        <v>2.76</v>
       </c>
       <c r="V132" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X132" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA132" t="n">
         <v>3.2</v>
       </c>
-      <c r="W132" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X132" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB132" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AD132" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AF132" t="n">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="AG132" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AI132" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AJ132" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AK132" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL132" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AM132" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR132" t="n">
         <v>1.8</v>
       </c>
-      <c r="AN132" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO132" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP132" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ132" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AS132" t="n">
-        <v>0.96</v>
+        <v>1.61</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
       <c r="AU132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA132" t="n">
         <v>3</v>
       </c>
-      <c r="AV132" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW132" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX132" t="n">
+      <c r="BB132" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC132" t="n">
         <v>8</v>
       </c>
-      <c r="AY132" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ132" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA132" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC132" t="n">
-        <v>7</v>
-      </c>
       <c r="BD132" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="BE132" t="n">
-        <v>8.949999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BF132" t="n">
-        <v>3.42</v>
+        <v>2.64</v>
       </c>
       <c r="BG132" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BH132" t="n">
-        <v>3.51</v>
+        <v>4.1</v>
       </c>
       <c r="BI132" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="BJ132" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="BK132" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="BL132" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="BM132" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BN132" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BO132" t="n">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
       <c r="BP132" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="133">
@@ -34351,7 +34351,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>8193692</v>
+        <v>8193731</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -34371,31 +34371,31 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -34404,101 +34404,101 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="Q156" t="n">
         <v>2.2</v>
       </c>
       <c r="R156" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S156" t="n">
-        <v>5.82</v>
+        <v>5.72</v>
       </c>
       <c r="T156" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="U156" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="V156" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="W156" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X156" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AA156" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AB156" t="n">
-        <v>5.2</v>
+        <v>4.97</v>
       </c>
       <c r="AC156" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD156" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF156" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AG156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI156" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH156" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI156" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ156" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AK156" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL156" t="n">
         <v>1.25</v>
       </c>
       <c r="AM156" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AN156" t="n">
-        <v>0.88</v>
+        <v>1.78</v>
       </c>
       <c r="AO156" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP156" t="n">
-        <v>0.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="AU156" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV156" t="n">
         <v>2</v>
@@ -34510,28 +34510,28 @@
         <v>7</v>
       </c>
       <c r="AY156" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ156" t="n">
         <v>9</v>
       </c>
       <c r="BA156" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB156" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BC156" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BD156" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="BE156" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="BF156" t="n">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="BG156" t="n">
         <v>1.13</v>
@@ -34540,13 +34540,13 @@
         <v>4.32</v>
       </c>
       <c r="BI156" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BJ156" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="BK156" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="BL156" t="n">
         <v>2.17</v>
@@ -34569,7 +34569,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>8193731</v>
+        <v>8193692</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -34589,31 +34589,31 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -34622,101 +34622,101 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q157" t="n">
         <v>2.2</v>
       </c>
       <c r="R157" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S157" t="n">
-        <v>5.72</v>
+        <v>5.82</v>
       </c>
       <c r="T157" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="U157" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V157" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="W157" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X157" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z157" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AA157" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="AB157" t="n">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD157" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF157" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AG157" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI157" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL157" t="n">
         <v>1.25</v>
       </c>
       <c r="AM157" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.78</v>
+        <v>0.88</v>
       </c>
       <c r="AO157" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.67</v>
+        <v>0.92</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="AU157" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV157" t="n">
         <v>2</v>
@@ -34728,28 +34728,28 @@
         <v>7</v>
       </c>
       <c r="AY157" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ157" t="n">
         <v>9</v>
       </c>
       <c r="BA157" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BB157" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BC157" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BD157" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="BE157" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF157" t="n">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="BG157" t="n">
         <v>1.13</v>
@@ -34758,13 +34758,13 @@
         <v>4.32</v>
       </c>
       <c r="BI157" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BJ157" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="BK157" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="BL157" t="n">
         <v>2.17</v>
@@ -35441,7 +35441,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>8193690</v>
+        <v>8193676</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -35461,197 +35461,197 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K161" t="n">
         <v>1</v>
       </c>
       <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
         <v>2</v>
-      </c>
-      <c r="M161" t="n">
-        <v>1</v>
       </c>
       <c r="N161" t="n">
         <v>3</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>['32', '74']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['43', '89']</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="R161" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S161" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T161" t="n">
         <v>1.4</v>
       </c>
       <c r="U161" t="n">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="V161" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="W161" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X161" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z161" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AA161" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AB161" t="n">
-        <v>3.73</v>
+        <v>3.15</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AD161" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AE161" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK161" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF161" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI161" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ161" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK161" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AL161" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AM161" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AN161" t="n">
-        <v>1.13</v>
+        <v>1.88</v>
       </c>
       <c r="AO161" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AP161" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ161" t="n">
         <v>1.42</v>
       </c>
-      <c r="AQ161" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AR161" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AT161" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="AU161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW161" t="n">
         <v>3</v>
       </c>
-      <c r="AV161" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW161" t="n">
-        <v>12</v>
-      </c>
       <c r="AX161" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB161" t="n">
         <v>5</v>
       </c>
-      <c r="AY161" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ161" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB161" t="n">
+      <c r="BC161" t="n">
         <v>9</v>
       </c>
-      <c r="BC161" t="n">
-        <v>15</v>
-      </c>
       <c r="BD161" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="BE161" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BF161" t="n">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="BG161" t="n">
         <v>1.19</v>
       </c>
       <c r="BH161" t="n">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="BI161" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="BJ161" t="n">
-        <v>2.83</v>
+        <v>2.49</v>
       </c>
       <c r="BK161" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="BL161" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="BM161" t="n">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="BN161" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="BO161" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="BP161" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="162">
@@ -35659,7 +35659,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>8193676</v>
+        <v>8193690</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -35679,197 +35679,197 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
         <v>1</v>
       </c>
       <c r="L162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N162" t="n">
         <v>3</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['32', '74']</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>['43', '89']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="R162" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S162" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T162" t="n">
         <v>1.4</v>
       </c>
       <c r="U162" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="V162" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="W162" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X162" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y162" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z162" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="AA162" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="AB162" t="n">
-        <v>3.15</v>
+        <v>3.73</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AD162" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF162" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI162" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AJ162" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AK162" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL162" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AM162" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AN162" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="AO162" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AT162" t="n">
-        <v>3.13</v>
+        <v>3.24</v>
       </c>
       <c r="AU162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA162" t="n">
         <v>6</v>
       </c>
-      <c r="AW162" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX162" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY162" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ162" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA162" t="n">
-        <v>4</v>
-      </c>
       <c r="BB162" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BC162" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE162" t="n">
         <v>9</v>
       </c>
-      <c r="BD162" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BE162" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="BF162" t="n">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="BG162" t="n">
         <v>1.19</v>
       </c>
       <c r="BH162" t="n">
-        <v>3.74</v>
+        <v>4.18</v>
       </c>
       <c r="BI162" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="BJ162" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="BK162" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BL162" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="BM162" t="n">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="BN162" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BO162" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="BP162" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="163">
@@ -36967,7 +36967,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>8193725</v>
+        <v>8193718</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -36987,12 +36987,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -37005,125 +37005,125 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N168" t="n">
         <v>1</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R168" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S168" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V168" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X168" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z168" t="n">
         <v>2.6</v>
       </c>
-      <c r="T168" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U168" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V168" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W168" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X168" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y168" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z168" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AA168" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AD168" t="n">
-        <v>8.4</v>
+        <v>7.23</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AF168" t="n">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="AG168" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="AH168" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AI168" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AJ168" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AK168" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AO168" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL168" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM168" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN168" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO168" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AP168" t="n">
-        <v>1.83</v>
+        <v>0.67</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.69</v>
+        <v>3.34</v>
       </c>
       <c r="AU168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV168" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW168" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY168" t="n">
         <v>7</v>
@@ -37132,52 +37132,52 @@
         <v>9</v>
       </c>
       <c r="BA168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC168" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD168" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="BE168" t="n">
-        <v>6.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF168" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="BG168" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BH168" t="n">
-        <v>3.86</v>
+        <v>3.52</v>
       </c>
       <c r="BI168" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="BJ168" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="BK168" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="BL168" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="BM168" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="BN168" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="BO168" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="BP168" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="169">
@@ -37185,7 +37185,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>8193718</v>
+        <v>8193725</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -37205,12 +37205,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -37223,125 +37223,125 @@
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
         <v>1</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
       <c r="Q169" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R169" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S169" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V169" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X169" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z169" t="n">
         <v>3.35</v>
       </c>
-      <c r="T169" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U169" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V169" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="W169" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X169" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Y169" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z169" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AA169" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU169" t="n">
         <v>3</v>
       </c>
-      <c r="AB169" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC169" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD169" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="AE169" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF169" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AG169" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH169" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI169" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ169" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK169" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL169" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM169" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN169" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AO169" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP169" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AQ169" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR169" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS169" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AT169" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AU169" t="n">
-        <v>1</v>
-      </c>
       <c r="AV169" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW169" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX169" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY169" t="n">
         <v>7</v>
@@ -37350,52 +37350,52 @@
         <v>9</v>
       </c>
       <c r="BA169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB169" t="n">
         <v>4</v>
       </c>
-      <c r="BB169" t="n">
-        <v>5</v>
-      </c>
       <c r="BC169" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD169" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="BE169" t="n">
-        <v>8.199999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="BF169" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="BG169" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BH169" t="n">
-        <v>3.52</v>
+        <v>3.86</v>
       </c>
       <c r="BI169" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="BJ169" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="BK169" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="BL169" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="BM169" t="n">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="BN169" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="BO169" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="BP169" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="170">
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>8193702</v>
+        <v>8193781</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,12 +42655,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -42676,10 +42676,10 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -42688,23 +42688,23 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>['49', '79', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>3.25</v>
+        <v>4.84</v>
       </c>
       <c r="R194" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="S194" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="T194" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U194" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="V194" t="n">
         <v>3.1</v>
@@ -42713,43 +42713,43 @@
         <v>1.31</v>
       </c>
       <c r="X194" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="Y194" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z194" t="n">
-        <v>2.79</v>
+        <v>3.98</v>
       </c>
       <c r="AA194" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AB194" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="AC194" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AD194" t="n">
-        <v>7.5</v>
+        <v>6.35</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF194" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AG194" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AH194" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI194" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AJ194" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AK194" t="n">
         <v>1.36</v>
@@ -42758,94 +42758,94 @@
         <v>0</v>
       </c>
       <c r="AM194" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AN194" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AO194" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AQ194" t="n">
-        <v>2.33</v>
+        <v>1.42</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AT194" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AU194" t="n">
         <v>2</v>
       </c>
       <c r="AV194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW194" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX194" t="n">
         <v>7</v>
       </c>
       <c r="AY194" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA194" t="n">
         <v>8</v>
       </c>
-      <c r="AZ194" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA194" t="n">
-        <v>4</v>
-      </c>
       <c r="BB194" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC194" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BD194" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="BE194" t="n">
-        <v>7.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF194" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BH194" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="BK194" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="BL194" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.49</v>
+        <v>2.22</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="BO194" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="195">
@@ -43071,7 +43071,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>8193781</v>
+        <v>8193702</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -43091,12 +43091,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -43112,10 +43112,10 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -43124,23 +43124,23 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '79', '81']</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>4.84</v>
+        <v>3.25</v>
       </c>
       <c r="R196" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="S196" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="T196" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U196" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="V196" t="n">
         <v>3.1</v>
@@ -43149,43 +43149,43 @@
         <v>1.31</v>
       </c>
       <c r="X196" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="Y196" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z196" t="n">
-        <v>3.98</v>
+        <v>2.79</v>
       </c>
       <c r="AA196" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="AB196" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AD196" t="n">
-        <v>6.35</v>
+        <v>7.5</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF196" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AG196" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AH196" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI196" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ196" t="n">
         <v>1.88</v>
-      </c>
-      <c r="AJ196" t="n">
-        <v>1.82</v>
       </c>
       <c r="AK196" t="n">
         <v>1.36</v>
@@ -43194,94 +43194,94 @@
         <v>0</v>
       </c>
       <c r="AM196" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AN196" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AO196" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.42</v>
+        <v>2.33</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AT196" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AU196" t="n">
         <v>2</v>
       </c>
       <c r="AV196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW196" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX196" t="n">
         <v>7</v>
       </c>
       <c r="AY196" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ196" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA196" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BB196" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BC196" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="BD196" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="BE196" t="n">
-        <v>8.4</v>
+        <v>7.03</v>
       </c>
       <c r="BF196" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL196" t="n">
         <v>1.77</v>
       </c>
-      <c r="BG196" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH196" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BI196" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BJ196" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BK196" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL196" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BM196" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="BN196" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="BO196" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="BP196" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="197">
@@ -46488,19 +46488,19 @@
         <v>2.88</v>
       </c>
       <c r="AU211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW211" t="n">
         <v>4</v>
       </c>
       <c r="AX211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY211" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ211" t="n">
         <v>8</v>
@@ -47363,19 +47363,19 @@
         <v>4</v>
       </c>
       <c r="AV215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW215" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ215" t="n">
         <v>8</v>
-      </c>
-      <c r="AX215" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY215" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ215" t="n">
-        <v>6</v>
       </c>
       <c r="BA215" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
@@ -47581,19 +47581,19 @@
         <v>2</v>
       </c>
       <c r="AV216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX216" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ216" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA216" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Portugal LigaPro_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.08</v>
@@ -2440,7 +2440,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.67</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.75</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.33</v>
@@ -5492,7 +5492,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR23" t="n">
         <v>1.19</v>
@@ -5710,7 +5710,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR24" t="n">
         <v>0.92</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.42</v>
@@ -6800,7 +6800,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR29" t="n">
         <v>1.24</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.33</v>
@@ -8108,7 +8108,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
         <v>1.05</v>
@@ -9198,7 +9198,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR40" t="n">
         <v>1.64</v>
@@ -9413,7 +9413,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.42</v>
@@ -9852,7 +9852,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR43" t="n">
         <v>1.36</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.25</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR46" t="n">
         <v>1.24</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.75</v>
@@ -11378,7 +11378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR50" t="n">
         <v>2.57</v>
@@ -12468,7 +12468,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR55" t="n">
         <v>1.58</v>
@@ -12686,7 +12686,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR56" t="n">
         <v>1.94</v>
@@ -12901,7 +12901,7 @@
         <v>1.67</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.33</v>
@@ -13119,7 +13119,7 @@
         <v>1.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.33</v>
@@ -13340,7 +13340,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR59" t="n">
         <v>1.1</v>
@@ -13555,10 +13555,10 @@
         <v>0.67</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR60" t="n">
         <v>1.23</v>
@@ -14863,7 +14863,7 @@
         <v>0.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.25</v>
@@ -17043,7 +17043,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.25</v>
@@ -17261,10 +17261,10 @@
         <v>1.75</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR77" t="n">
         <v>2.07</v>
@@ -17482,7 +17482,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
         <v>2.31</v>
@@ -17700,7 +17700,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR79" t="n">
         <v>1.53</v>
@@ -18787,7 +18787,7 @@
         <v>2.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84" t="n">
         <v>2.33</v>
@@ -19880,7 +19880,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR89" t="n">
         <v>1.88</v>
@@ -20095,7 +20095,7 @@
         <v>2.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.42</v>
@@ -20313,7 +20313,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.67</v>
@@ -20749,7 +20749,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.25</v>
@@ -20970,7 +20970,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR94" t="n">
         <v>1.41</v>
@@ -21188,7 +21188,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR95" t="n">
         <v>1.54</v>
@@ -21406,7 +21406,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR96" t="n">
         <v>1.74</v>
@@ -21842,7 +21842,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR98" t="n">
         <v>1.52</v>
@@ -22493,7 +22493,7 @@
         <v>2</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.42</v>
@@ -23147,7 +23147,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.5</v>
@@ -23801,7 +23801,7 @@
         <v>2.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ107" t="n">
         <v>2.33</v>
@@ -24022,7 +24022,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR108" t="n">
         <v>2.09</v>
@@ -24891,7 +24891,7 @@
         <v>1.5</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.33</v>
@@ -25330,7 +25330,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR114" t="n">
         <v>1.79</v>
@@ -26202,7 +26202,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR118" t="n">
         <v>1.83</v>
@@ -26417,10 +26417,10 @@
         <v>0.5</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR119" t="n">
         <v>1.5</v>
@@ -26853,7 +26853,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.33</v>
@@ -27728,7 +27728,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR125" t="n">
         <v>1.9</v>
@@ -28161,7 +28161,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.5</v>
@@ -28815,7 +28815,7 @@
         <v>1</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.33</v>
@@ -29036,7 +29036,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR131" t="n">
         <v>1.84</v>
@@ -29254,7 +29254,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR132" t="n">
         <v>1.8</v>
@@ -30123,10 +30123,10 @@
         <v>1.43</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR136" t="n">
         <v>1.35</v>
@@ -30998,7 +30998,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR140" t="n">
         <v>1.46</v>
@@ -32088,7 +32088,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR145" t="n">
         <v>1.9</v>
@@ -32303,10 +32303,10 @@
         <v>0.75</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR146" t="n">
         <v>1.48</v>
@@ -32742,7 +32742,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR148" t="n">
         <v>1.65</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.75</v>
@@ -33393,7 +33393,7 @@
         <v>2.57</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ151" t="n">
         <v>2.33</v>
@@ -33829,7 +33829,7 @@
         <v>1.13</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.25</v>
@@ -34050,7 +34050,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR154" t="n">
         <v>1.68</v>
@@ -34919,7 +34919,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.33</v>
@@ -35576,7 +35576,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR161" t="n">
         <v>1.75</v>
@@ -36230,7 +36230,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR164" t="n">
         <v>1.55</v>
@@ -36445,7 +36445,7 @@
         <v>1.88</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.58</v>
@@ -37099,7 +37099,7 @@
         <v>1.33</v>
       </c>
       <c r="AP168" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.25</v>
@@ -37538,7 +37538,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR170" t="n">
         <v>1.54</v>
@@ -37753,7 +37753,7 @@
         <v>0.89</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ171" t="n">
         <v>1</v>
@@ -38407,7 +38407,7 @@
         <v>1.22</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.5</v>
@@ -38846,7 +38846,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR176" t="n">
         <v>1.77</v>
@@ -39936,7 +39936,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR181" t="n">
         <v>1.22</v>
@@ -40151,7 +40151,7 @@
         <v>0.8</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ182" t="n">
         <v>1</v>
@@ -40590,7 +40590,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR184" t="n">
         <v>1.81</v>
@@ -40805,7 +40805,7 @@
         <v>1.3</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.33</v>
@@ -41459,7 +41459,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.08</v>
@@ -42770,7 +42770,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR194" t="n">
         <v>1.63</v>
@@ -43639,7 +43639,7 @@
         <v>1.9</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.58</v>
@@ -44511,7 +44511,7 @@
         <v>1.18</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.33</v>
@@ -44947,10 +44947,10 @@
         <v>1.45</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR204" t="n">
         <v>1.57</v>
@@ -45165,10 +45165,10 @@
         <v>1.18</v>
       </c>
       <c r="AP205" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR205" t="n">
         <v>1.54</v>
@@ -45604,7 +45604,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR207" t="n">
         <v>1.21</v>
@@ -47345,7 +47345,7 @@
         <v>1.09</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.08</v>
@@ -47642,6 +47642,878 @@
       </c>
       <c r="BP216" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8193708</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46087.625</v>
+      </c>
+      <c r="F217" t="n">
+        <v>25</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>GD Chaves</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>1</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S217" t="n">
+        <v>3</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U217" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X217" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8193710</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46088.33333333334</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Torreense</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>2</v>
+      </c>
+      <c r="K218" t="n">
+        <v>2</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>3</v>
+      </c>
+      <c r="N218" t="n">
+        <v>3</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>['19', '27', '88']</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>4</v>
+      </c>
+      <c r="R218" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S218" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V218" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X218" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8193695</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46088.45833333334</v>
+      </c>
+      <c r="F219" t="n">
+        <v>25</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Portimonense</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Paços de Ferreira</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>2</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>2</v>
+      </c>
+      <c r="L219" t="n">
+        <v>2</v>
+      </c>
+      <c r="M219" t="n">
+        <v>3</v>
+      </c>
+      <c r="N219" t="n">
+        <v>5</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>['19', '43']</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>['46', '53', '70']</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R219" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S219" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X219" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8193922</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46088.52083333334</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>FC Penafiel</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['90+6']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S220" t="n">
+        <v>3</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V220" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X220" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
